--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2301-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2301-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF929055-C608-4548-8A77-B0622EDC9ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA427C82-8DD9-483B-9FC5-8E8B3C5075D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{47119FF5-D1F2-46A4-9F48-62834C280985}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6470ACAA-D7AC-4688-BB9F-1F31A32C908C}"/>
   </bookViews>
   <sheets>
     <sheet name="2301-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1553,30 +1553,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1C0A34-C7FA-4EE8-9135-CEB8D31A7A25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E590F9A-F59F-4736-8117-1C4B4A173BFF}">
   <dimension ref="A1:X66"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1766,7 +1766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2021</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2020</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>29</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>29</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2019</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2018</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2017</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2016</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2015</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2014</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2013</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2012</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2011</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>2010</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>2009</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>2008</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>2007</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>2006</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>2005</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>2004</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>2003</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>2002</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="35">
         <v>2001</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>2000</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="35">
         <v>1999</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="37">
         <v>1998</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="35">
         <v>1997</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="37">
         <v>1996</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="35">
         <v>1995</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="37">
         <v>1994</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="35">
         <v>1993</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="37">
         <v>1992</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
         <v>72</v>
       </c>
